--- a/partecipanti-esercitazione.xlsx
+++ b/partecipanti-esercitazione.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\stpc-analisi-dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BE87F1-E4A9-435D-85FA-463E4EDDF34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAE4E83-A7A4-49AF-BB95-B192EFA1D8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="606">
   <si>
     <t>Nome</t>
   </si>
@@ -1835,6 +1835,9 @@
   </si>
   <si>
     <t>253666</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -2250,6 +2253,9 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -2294,6 +2300,9 @@
       <c r="C7" t="s">
         <v>20</v>
       </c>
+      <c r="D7" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -2305,6 +2314,9 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
+      <c r="D8" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -2349,6 +2361,9 @@
       <c r="C12" t="s">
         <v>35</v>
       </c>
+      <c r="D12" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -2382,6 +2397,9 @@
       <c r="C15" t="s">
         <v>43</v>
       </c>
+      <c r="D15" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -2394,7 +2412,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -2405,7 +2423,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -2415,8 +2433,11 @@
       <c r="C18" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -2427,7 +2448,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -2437,8 +2458,11 @@
       <c r="C20" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -2449,7 +2473,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -2460,7 +2484,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -2471,7 +2495,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -2482,7 +2506,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -2493,7 +2517,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -2504,7 +2528,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -2515,7 +2539,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -2526,7 +2550,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2537,7 +2561,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>84</v>
       </c>
@@ -2548,7 +2572,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -2559,7 +2583,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -2570,7 +2594,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>93</v>
       </c>
@@ -2580,8 +2604,11 @@
       <c r="C33" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -2592,7 +2619,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -2603,7 +2630,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -2614,7 +2641,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>104</v>
       </c>
@@ -2625,7 +2652,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>107</v>
       </c>
@@ -2636,7 +2663,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -2646,8 +2673,11 @@
       <c r="C39" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -2658,7 +2688,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>115</v>
       </c>
@@ -2669,7 +2699,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>118</v>
       </c>
@@ -2680,7 +2710,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>121</v>
       </c>
@@ -2691,7 +2721,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>124</v>
       </c>
@@ -2702,7 +2732,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>127</v>
       </c>
@@ -2712,8 +2742,11 @@
       <c r="C45" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>130</v>
       </c>
@@ -2723,8 +2756,11 @@
       <c r="C46" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>101</v>
       </c>
@@ -2735,7 +2771,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -2746,7 +2782,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>138</v>
       </c>
@@ -2756,8 +2792,11 @@
       <c r="C49" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>141</v>
       </c>
@@ -2768,7 +2807,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>144</v>
       </c>
@@ -2779,7 +2818,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -2790,7 +2829,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>149</v>
       </c>
@@ -2801,7 +2840,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>152</v>
       </c>
@@ -2811,8 +2850,11 @@
       <c r="C54" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -2823,7 +2865,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>157</v>
       </c>
@@ -2834,7 +2876,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>36</v>
       </c>
@@ -2845,7 +2887,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -2856,7 +2898,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>164</v>
       </c>
@@ -2867,7 +2909,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -2878,7 +2920,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>21</v>
       </c>
@@ -2889,7 +2931,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>171</v>
       </c>
@@ -2900,7 +2942,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>174</v>
       </c>
@@ -2910,8 +2952,11 @@
       <c r="C63" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>177</v>
       </c>
@@ -2922,7 +2967,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>180</v>
       </c>
@@ -2933,7 +2978,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>180</v>
       </c>
@@ -2944,7 +2989,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -2954,8 +2999,11 @@
       <c r="C67" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -2966,7 +3014,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>189</v>
       </c>
@@ -2977,7 +3025,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>192</v>
       </c>
@@ -2988,7 +3036,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -2999,7 +3047,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>164</v>
       </c>
@@ -3009,8 +3057,11 @@
       <c r="C72" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>130</v>
       </c>
@@ -3021,7 +3072,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>201</v>
       </c>
@@ -3029,7 +3080,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>203</v>
       </c>
@@ -3040,7 +3091,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -3051,7 +3102,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>208</v>
       </c>
@@ -3062,7 +3113,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -3072,8 +3123,11 @@
       <c r="C78" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>213</v>
       </c>
@@ -3084,7 +3138,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>216</v>
       </c>
@@ -3271,7 +3325,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -3282,7 +3336,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>171</v>
       </c>
@@ -3293,7 +3347,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>264</v>
       </c>
@@ -3304,7 +3358,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>73</v>
       </c>
@@ -3315,7 +3369,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>269</v>
       </c>
@@ -3326,7 +3380,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>272</v>
       </c>
@@ -3336,8 +3390,11 @@
       <c r="C102" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D102" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>79</v>
       </c>
@@ -3347,8 +3404,11 @@
       <c r="C103" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D103" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>277</v>
       </c>
@@ -3359,7 +3419,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>280</v>
       </c>
@@ -3370,7 +3430,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>283</v>
       </c>
@@ -3380,8 +3440,11 @@
       <c r="C106" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D106" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>203</v>
       </c>
@@ -3392,7 +3455,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>288</v>
       </c>
@@ -3403,7 +3466,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>59</v>
       </c>
@@ -3414,7 +3477,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>53</v>
       </c>
@@ -3425,7 +3488,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>295</v>
       </c>
@@ -3436,7 +3499,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>298</v>
       </c>
@@ -3447,7 +3510,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>301</v>
       </c>
@@ -3457,8 +3520,11 @@
       <c r="C113" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D113" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>304</v>
       </c>
@@ -3469,7 +3535,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>307</v>
       </c>
@@ -3480,7 +3546,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>310</v>
       </c>
@@ -3491,7 +3557,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>53</v>
       </c>
@@ -3502,7 +3568,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>171</v>
       </c>
@@ -3512,8 +3578,11 @@
       <c r="C118" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D118" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>317</v>
       </c>
@@ -3524,7 +3593,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>320</v>
       </c>
@@ -3534,8 +3603,11 @@
       <c r="C120" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D120" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>90</v>
       </c>
@@ -3546,7 +3618,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>325</v>
       </c>
@@ -3557,7 +3629,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>62</v>
       </c>
@@ -3568,7 +3640,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>330</v>
       </c>
@@ -3578,8 +3650,11 @@
       <c r="C124" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D124" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -3590,7 +3665,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>141</v>
       </c>
@@ -3600,8 +3675,11 @@
       <c r="C126" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D126" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>337</v>
       </c>
@@ -3612,7 +3690,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>164</v>
       </c>
@@ -3622,8 +3700,11 @@
       <c r="C128" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D128" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>342</v>
       </c>
@@ -3634,7 +3715,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>345</v>
       </c>
@@ -3644,8 +3725,11 @@
       <c r="C130" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D130" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>90</v>
       </c>
@@ -3655,8 +3739,11 @@
       <c r="C131" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D131" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>350</v>
       </c>
@@ -3666,8 +3753,11 @@
       <c r="C132" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D132" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>222</v>
       </c>
@@ -3678,7 +3768,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>355</v>
       </c>
@@ -3688,8 +3778,11 @@
       <c r="C134" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D134" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>239</v>
       </c>
@@ -3699,8 +3792,11 @@
       <c r="C135" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D135" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>360</v>
       </c>
@@ -3711,7 +3807,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>79</v>
       </c>
@@ -3722,7 +3818,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>365</v>
       </c>
@@ -3733,7 +3829,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>90</v>
       </c>
@@ -3744,7 +3840,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>370</v>
       </c>
@@ -3755,7 +3851,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>373</v>
       </c>
@@ -3766,7 +3862,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>376</v>
       </c>
@@ -3777,7 +3873,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>222</v>
       </c>
@@ -3787,8 +3883,11 @@
       <c r="C143" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D143" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>222</v>
       </c>
@@ -3798,8 +3897,11 @@
       <c r="C144" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D144" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>383</v>
       </c>
@@ -3807,7 +3909,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>385</v>
       </c>
@@ -3817,8 +3919,11 @@
       <c r="C146" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D146" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>388</v>
       </c>
@@ -3828,8 +3933,11 @@
       <c r="C147" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D147" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>391</v>
       </c>
@@ -3840,7 +3948,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>317</v>
       </c>
@@ -3851,7 +3959,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>325</v>
       </c>
@@ -3862,7 +3970,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>398</v>
       </c>
@@ -3872,8 +3980,11 @@
       <c r="C151" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D151" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -3883,8 +3994,11 @@
       <c r="C152" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D152" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>403</v>
       </c>
@@ -3894,8 +4008,11 @@
       <c r="C153" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D153" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>36</v>
       </c>
@@ -3905,8 +4022,11 @@
       <c r="C154" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D154" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>408</v>
       </c>
@@ -3917,7 +4037,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>411</v>
       </c>
@@ -3928,7 +4048,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>414</v>
       </c>
@@ -3938,8 +4058,11 @@
       <c r="C157" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D157" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>417</v>
       </c>
@@ -3950,7 +4073,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>420</v>
       </c>
@@ -3961,7 +4084,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>423</v>
       </c>
@@ -3971,8 +4094,11 @@
       <c r="C160" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D160" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>426</v>
       </c>
@@ -3980,7 +4106,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>428</v>
       </c>
@@ -3990,8 +4116,11 @@
       <c r="C162" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D162" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>33</v>
       </c>
@@ -4001,8 +4130,11 @@
       <c r="C163" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D163" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>433</v>
       </c>
@@ -4013,7 +4145,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>342</v>
       </c>
@@ -4024,7 +4156,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>438</v>
       </c>
@@ -4035,7 +4167,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>441</v>
       </c>
@@ -4046,7 +4178,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>444</v>
       </c>
@@ -4057,7 +4189,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>447</v>
       </c>
@@ -4068,7 +4200,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>164</v>
       </c>
@@ -4078,8 +4210,11 @@
       <c r="C170" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D170" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>452</v>
       </c>
@@ -4090,7 +4225,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>47</v>
       </c>
@@ -4101,7 +4236,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>317</v>
       </c>
@@ -4112,7 +4247,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>458</v>
       </c>
@@ -4122,8 +4257,11 @@
       <c r="C174" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D174" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>36</v>
       </c>
@@ -4134,7 +4272,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>463</v>
       </c>
@@ -4144,8 +4282,11 @@
       <c r="C176" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D176" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>466</v>
       </c>
@@ -4156,7 +4297,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>469</v>
       </c>
@@ -4166,8 +4307,11 @@
       <c r="C178" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D178" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>472</v>
       </c>
@@ -4178,7 +4322,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>96</v>
       </c>
@@ -4189,7 +4333,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>47</v>
       </c>
@@ -4200,7 +4344,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>56</v>
       </c>
@@ -4211,7 +4355,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>62</v>
       </c>
@@ -4222,7 +4366,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>254</v>
       </c>
@@ -4233,7 +4377,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>463</v>
       </c>
@@ -4243,8 +4387,11 @@
       <c r="C185" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D185" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>486</v>
       </c>
@@ -4255,7 +4402,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>33</v>
       </c>
@@ -4266,7 +4413,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>491</v>
       </c>
@@ -4277,7 +4424,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>494</v>
       </c>
@@ -4287,8 +4434,11 @@
       <c r="C189" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D189" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>385</v>
       </c>
@@ -4298,8 +4448,11 @@
       <c r="C190" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D190" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>497</v>
       </c>
@@ -4309,8 +4462,11 @@
       <c r="C191" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D191" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -4320,8 +4476,11 @@
       <c r="C192" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D192" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>225</v>
       </c>
@@ -4332,7 +4491,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>504</v>
       </c>
@@ -4342,8 +4501,11 @@
       <c r="C194" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D194" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>507</v>
       </c>
@@ -4354,7 +4516,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>510</v>
       </c>
@@ -4365,7 +4527,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>317</v>
       </c>
@@ -4375,8 +4537,11 @@
       <c r="C197" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D197" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>24</v>
       </c>
@@ -4387,7 +4552,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>517</v>
       </c>
@@ -4398,7 +4563,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>254</v>
       </c>
@@ -4409,7 +4574,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>522</v>
       </c>
@@ -4420,7 +4585,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>174</v>
       </c>
@@ -4430,8 +4595,11 @@
       <c r="C202" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D202" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>527</v>
       </c>
@@ -4441,8 +4609,11 @@
       <c r="C203" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D203" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>441</v>
       </c>
@@ -4452,8 +4623,11 @@
       <c r="C204" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D204" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>532</v>
       </c>
@@ -4464,7 +4638,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>535</v>
       </c>
@@ -4474,8 +4648,11 @@
       <c r="C206" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D206" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>538</v>
       </c>
@@ -4485,8 +4662,11 @@
       <c r="C207" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D207" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>33</v>
       </c>
@@ -4496,8 +4676,11 @@
       <c r="C208" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D208" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>543</v>
       </c>
@@ -4508,7 +4691,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>546</v>
       </c>
@@ -4519,7 +4702,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>549</v>
       </c>
@@ -4530,7 +4713,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>124</v>
       </c>
@@ -4541,7 +4724,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>554</v>
       </c>
@@ -4551,8 +4734,11 @@
       <c r="C213" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D213" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>557</v>
       </c>
@@ -4562,8 +4748,11 @@
       <c r="C214" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D214" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>246</v>
       </c>
@@ -4574,7 +4763,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>62</v>
       </c>
@@ -4585,7 +4774,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>222</v>
       </c>
@@ -4595,8 +4784,11 @@
       <c r="C217" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D217" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>566</v>
       </c>
@@ -4606,8 +4798,11 @@
       <c r="C218" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D218" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>569</v>
       </c>
@@ -4617,8 +4812,11 @@
       <c r="C219" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D219" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>62</v>
       </c>
@@ -4629,7 +4827,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>50</v>
       </c>
@@ -4639,8 +4837,11 @@
       <c r="C221" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D221" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>365</v>
       </c>
@@ -4651,7 +4852,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>578</v>
       </c>
@@ -4661,8 +4862,11 @@
       <c r="C223" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D223" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>376</v>
       </c>
@@ -4672,8 +4876,11 @@
       <c r="C224" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D224" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>583</v>
       </c>
@@ -4684,7 +4891,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>586</v>
       </c>
@@ -4694,8 +4901,11 @@
       <c r="C226" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D226" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>589</v>
       </c>
@@ -4705,8 +4915,11 @@
       <c r="C227" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E227" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>592</v>
       </c>
@@ -4717,7 +4930,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>595</v>
       </c>
@@ -4727,8 +4940,11 @@
       <c r="C229" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D229" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>598</v>
       </c>
@@ -4739,7 +4955,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>383</v>
       </c>
@@ -4749,8 +4965,11 @@
       <c r="C231" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D231" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>171</v>
       </c>
@@ -4759,6 +4978,9 @@
       </c>
       <c r="C232" t="s">
         <v>604</v>
+      </c>
+      <c r="D232" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/partecipanti-esercitazione.xlsx
+++ b/partecipanti-esercitazione.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\stpc-analisi-dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAE4E83-A7A4-49AF-BB95-B192EFA1D8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA98773-84B6-405F-AC8E-F3EA1A8698E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="607">
   <si>
     <t>Nome</t>
   </si>
@@ -1838,6 +1838,9 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -2328,6 +2331,9 @@
       <c r="C9" t="s">
         <v>26</v>
       </c>
+      <c r="D9" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -2472,6 +2478,9 @@
       <c r="C21" t="s">
         <v>61</v>
       </c>
+      <c r="D21" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
@@ -2806,6 +2815,9 @@
       <c r="C50" t="s">
         <v>143</v>
       </c>
+      <c r="D50" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
@@ -2908,6 +2920,9 @@
       <c r="C59" t="s">
         <v>166</v>
       </c>
+      <c r="D59" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
@@ -3046,6 +3061,9 @@
       <c r="C71" t="s">
         <v>196</v>
       </c>
+      <c r="D71" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
@@ -3071,6 +3089,9 @@
       <c r="C73" t="s">
         <v>200</v>
       </c>
+      <c r="D73" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
@@ -3112,6 +3133,9 @@
       <c r="C77" t="s">
         <v>210</v>
       </c>
+      <c r="D77" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
@@ -3149,7 +3173,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>219</v>
       </c>
@@ -3160,7 +3184,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>222</v>
       </c>
@@ -3171,7 +3195,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>225</v>
       </c>
@@ -3182,7 +3206,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>228</v>
       </c>
@@ -3193,7 +3217,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>231</v>
       </c>
@@ -3204,7 +3228,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>234</v>
       </c>
@@ -3214,8 +3238,11 @@
       <c r="C86" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D86" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>33</v>
       </c>
@@ -3226,7 +3253,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>239</v>
       </c>
@@ -3237,7 +3264,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -3248,7 +3275,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>141</v>
       </c>
@@ -3259,7 +3286,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>246</v>
       </c>
@@ -3270,7 +3297,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -3281,7 +3308,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>251</v>
       </c>
@@ -3292,7 +3319,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>254</v>
       </c>
@@ -3303,7 +3330,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>56</v>
       </c>
@@ -3314,7 +3341,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>149</v>
       </c>
@@ -3346,6 +3373,9 @@
       <c r="C98" t="s">
         <v>263</v>
       </c>
+      <c r="D98" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
@@ -3806,6 +3836,9 @@
       <c r="C136" t="s">
         <v>362</v>
       </c>
+      <c r="D136" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
@@ -3817,6 +3850,9 @@
       <c r="C137" t="s">
         <v>364</v>
       </c>
+      <c r="D137" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
@@ -3828,6 +3864,9 @@
       <c r="C138" t="s">
         <v>367</v>
       </c>
+      <c r="D138" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
@@ -4401,6 +4440,9 @@
       <c r="C186" t="s">
         <v>488</v>
       </c>
+      <c r="D186" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
@@ -4490,6 +4532,9 @@
       <c r="C193" t="s">
         <v>503</v>
       </c>
+      <c r="D193" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
@@ -4826,6 +4871,9 @@
       <c r="C220" t="s">
         <v>573</v>
       </c>
+      <c r="D220" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
@@ -4928,6 +4976,9 @@
       </c>
       <c r="C228" t="s">
         <v>594</v>
+      </c>
+      <c r="D228" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">

--- a/partecipanti-esercitazione.xlsx
+++ b/partecipanti-esercitazione.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\stpc-analisi-dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA98773-84B6-405F-AC8E-F3EA1A8698E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63BC210-3966-4329-A17B-9506BD538B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="607">
   <si>
     <t>Nome</t>
   </si>
@@ -2898,6 +2898,9 @@
       <c r="C57" t="s">
         <v>161</v>
       </c>
+      <c r="D57" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
@@ -4453,6 +4456,9 @@
       </c>
       <c r="C187" t="s">
         <v>490</v>
+      </c>
+      <c r="D187" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">

--- a/partecipanti-esercitazione.xlsx
+++ b/partecipanti-esercitazione.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\stpc-analisi-dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63BC210-3966-4329-A17B-9506BD538B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476966AF-F8F3-465C-8EE3-5FB365EF423A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="607">
   <si>
     <t>Nome</t>
   </si>
@@ -1847,11 +1847,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1874,9 +1881,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2211,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:J232"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.4140625" bestFit="1" customWidth="1"/>
@@ -2345,6 +2353,9 @@
       <c r="C10" t="s">
         <v>29</v>
       </c>
+      <c r="D10" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -2649,6 +2660,9 @@
       <c r="C36" t="s">
         <v>103</v>
       </c>
+      <c r="D36" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
@@ -2696,6 +2710,9 @@
       <c r="C40" t="s">
         <v>114</v>
       </c>
+      <c r="D40" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
@@ -2948,6 +2965,9 @@
       <c r="C61" t="s">
         <v>170</v>
       </c>
+      <c r="D61" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -2985,7 +3005,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>180</v>
       </c>
@@ -2996,7 +3016,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>180</v>
       </c>
@@ -3006,8 +3026,9 @@
       <c r="C66" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -3021,7 +3042,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -3031,8 +3052,11 @@
       <c r="C68" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D68" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>189</v>
       </c>
@@ -3043,7 +3067,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>192</v>
       </c>
@@ -3054,7 +3078,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -3068,7 +3092,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>164</v>
       </c>
@@ -3082,7 +3106,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>130</v>
       </c>
@@ -3096,7 +3120,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>201</v>
       </c>
@@ -3104,7 +3128,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>203</v>
       </c>
@@ -3115,7 +3139,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -3126,7 +3150,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>208</v>
       </c>
@@ -3140,7 +3164,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -3154,7 +3178,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>213</v>
       </c>
@@ -3165,7 +3189,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>216</v>
       </c>
@@ -3230,6 +3254,9 @@
       <c r="C85" t="s">
         <v>233</v>
       </c>
+      <c r="D85" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
@@ -3365,6 +3392,9 @@
       <c r="C97" t="s">
         <v>261</v>
       </c>
+      <c r="D97" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
@@ -3747,6 +3777,9 @@
       <c r="C129" t="s">
         <v>344</v>
       </c>
+      <c r="D129" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
@@ -3892,6 +3925,9 @@
       <c r="C140" t="s">
         <v>372</v>
       </c>
+      <c r="D140" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
@@ -4219,6 +4255,9 @@
       <c r="C167" t="s">
         <v>443</v>
       </c>
+      <c r="D167" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
@@ -4623,6 +4662,9 @@
       </c>
       <c r="C200" t="s">
         <v>521</v>
+      </c>
+      <c r="D200" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">

--- a/partecipanti-esercitazione.xlsx
+++ b/partecipanti-esercitazione.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\stpc-analisi-dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476966AF-F8F3-465C-8EE3-5FB365EF423A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DE8C18-2B77-446A-8A79-2111FAE5BCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="607">
   <si>
     <t>Nome</t>
   </si>
@@ -2464,6 +2464,9 @@
       <c r="C19" t="s">
         <v>55</v>
       </c>
+      <c r="D19" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -2525,6 +2528,9 @@
       <c r="C24" t="s">
         <v>69</v>
       </c>
+      <c r="D24" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
@@ -2904,6 +2910,9 @@
       <c r="C56" t="s">
         <v>159</v>
       </c>
+      <c r="D56" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
@@ -3077,6 +3086,9 @@
       <c r="C70" t="s">
         <v>194</v>
       </c>
+      <c r="D70" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
@@ -3221,6 +3233,9 @@
       <c r="C82" t="s">
         <v>224</v>
       </c>
+      <c r="D82" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
@@ -3517,6 +3532,9 @@
       <c r="C107" t="s">
         <v>287</v>
       </c>
+      <c r="D107" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
@@ -4025,6 +4043,9 @@
       <c r="C148" t="s">
         <v>393</v>
       </c>
+      <c r="D148" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
@@ -4222,6 +4243,9 @@
       <c r="C164" t="s">
         <v>435</v>
       </c>
+      <c r="D164" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
@@ -4413,6 +4437,9 @@
       <c r="C180" t="s">
         <v>475</v>
       </c>
+      <c r="D180" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
@@ -4510,6 +4537,9 @@
       <c r="C188" t="s">
         <v>493</v>
       </c>
+      <c r="D188" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
@@ -4604,6 +4634,9 @@
       </c>
       <c r="C195" t="s">
         <v>509</v>
+      </c>
+      <c r="D195" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.35">
